--- a/outputs/Wheat_flour_(low_quality)_tukey_classification_matrix.xlsx
+++ b/outputs/Wheat_flour_(low_quality)_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="110">
   <si>
     <t>2020 May</t>
   </si>
@@ -343,55 +343,7 @@
     <t>Minimal</t>
   </si>
   <si>
-    <t>Alert</t>
-  </si>
-  <si>
-    <t>Alarm</t>
-  </si>
-  <si>
-    <t>21%</t>
-  </si>
-  <si>
-    <t>24%</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>13%</t>
-  </si>
-  <si>
-    <t>30%</t>
-  </si>
-  <si>
-    <t>23%</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>27%</t>
-  </si>
-  <si>
-    <t>28%</t>
-  </si>
-  <si>
-    <t>3%</t>
-  </si>
-  <si>
-    <t>1%</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>7%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>31%</t>
   </si>
 </sst>
 </file>
@@ -1057,55 +1009,55 @@
         <v>108</v>
       </c>
       <c r="S2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ2" t="s">
         <v>108</v>
@@ -1219,13 +1171,13 @@
         <v>108</v>
       </c>
       <c r="BU2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV2" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="BW2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1284,55 +1236,55 @@
         <v>108</v>
       </c>
       <c r="S3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ3" t="s">
         <v>108</v>
@@ -1446,13 +1398,13 @@
         <v>108</v>
       </c>
       <c r="BU3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV3" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="BW3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1511,58 +1463,58 @@
         <v>108</v>
       </c>
       <c r="S4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK4" t="s">
         <v>108</v>
@@ -1673,13 +1625,13 @@
         <v>108</v>
       </c>
       <c r="BU4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BV4" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1738,58 +1690,58 @@
         <v>108</v>
       </c>
       <c r="S5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK5" t="s">
         <v>108</v>
@@ -1900,13 +1852,13 @@
         <v>108</v>
       </c>
       <c r="BU5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV5" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="BW5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1962,61 +1914,61 @@
         <v>108</v>
       </c>
       <c r="R6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK6" t="s">
         <v>108</v>
@@ -2127,13 +2079,13 @@
         <v>108</v>
       </c>
       <c r="BU6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV6" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW6" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2198,46 +2150,46 @@
         <v>108</v>
       </c>
       <c r="U7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI7" t="s">
         <v>108</v>
@@ -2354,13 +2306,13 @@
         <v>108</v>
       </c>
       <c r="BU7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV7" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="BW7" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2368,13 +2320,13 @@
         <v>81</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
         <v>108</v>
@@ -2419,61 +2371,61 @@
         <v>108</v>
       </c>
       <c r="S8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL8" t="s">
         <v>108</v>
@@ -2581,13 +2533,13 @@
         <v>108</v>
       </c>
       <c r="BU8" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BV8" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW8" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2646,58 +2598,58 @@
         <v>108</v>
       </c>
       <c r="S9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK9" t="s">
         <v>108</v>
@@ -2808,13 +2760,13 @@
         <v>108</v>
       </c>
       <c r="BU9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV9" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="BW9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2879,52 +2831,52 @@
         <v>108</v>
       </c>
       <c r="U10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK10" t="s">
         <v>108</v>
@@ -3035,13 +2987,13 @@
         <v>108</v>
       </c>
       <c r="BU10" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="BV10" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="BW10" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3100,19 +3052,19 @@
         <v>108</v>
       </c>
       <c r="S11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X11" t="s">
         <v>108</v>
@@ -3127,31 +3079,31 @@
         <v>108</v>
       </c>
       <c r="AB11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK11" t="s">
         <v>108</v>
@@ -3262,13 +3214,13 @@
         <v>108</v>
       </c>
       <c r="BU11" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="BV11" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="BW11" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:75">
@@ -3327,55 +3279,55 @@
         <v>108</v>
       </c>
       <c r="S12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ12" t="s">
         <v>108</v>
@@ -3489,13 +3441,13 @@
         <v>108</v>
       </c>
       <c r="BU12" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="BV12" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="BW12" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:75">
@@ -3554,64 +3506,64 @@
         <v>108</v>
       </c>
       <c r="S13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM13" t="s">
         <v>108</v>
@@ -3716,13 +3668,13 @@
         <v>108</v>
       </c>
       <c r="BU13" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BV13" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW13" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:75">
@@ -3781,58 +3733,58 @@
         <v>108</v>
       </c>
       <c r="S14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK14" t="s">
         <v>108</v>
@@ -3943,13 +3895,13 @@
         <v>108</v>
       </c>
       <c r="BU14" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV14" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="BW14" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:75">
@@ -4008,55 +3960,55 @@
         <v>108</v>
       </c>
       <c r="S15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ15" t="s">
         <v>108</v>
@@ -4170,13 +4122,13 @@
         <v>108</v>
       </c>
       <c r="BU15" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BV15" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="BW15" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:75">
@@ -4235,58 +4187,58 @@
         <v>108</v>
       </c>
       <c r="S16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK16" t="s">
         <v>108</v>
@@ -4397,13 +4349,13 @@
         <v>108</v>
       </c>
       <c r="BU16" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV16" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="BW16" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:75">
@@ -4462,52 +4414,52 @@
         <v>108</v>
       </c>
       <c r="S17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W17" t="s">
         <v>108</v>
       </c>
       <c r="X17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI17" t="s">
         <v>108</v>
@@ -4624,13 +4576,13 @@
         <v>108</v>
       </c>
       <c r="BU17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV17" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="BW17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:75">
@@ -4689,58 +4641,58 @@
         <v>108</v>
       </c>
       <c r="S18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK18" t="s">
         <v>108</v>
@@ -4851,13 +4803,13 @@
         <v>108</v>
       </c>
       <c r="BU18" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV18" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="BW18" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:75">
@@ -4919,61 +4871,61 @@
         <v>108</v>
       </c>
       <c r="T19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM19" t="s">
         <v>108</v>
@@ -5078,13 +5030,13 @@
         <v>108</v>
       </c>
       <c r="BU19" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV19" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW19" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:75">
@@ -5143,58 +5095,58 @@
         <v>108</v>
       </c>
       <c r="S20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK20" t="s">
         <v>108</v>
@@ -5305,13 +5257,13 @@
         <v>108</v>
       </c>
       <c r="BU20" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV20" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="BW20" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:75">
@@ -5373,67 +5325,67 @@
         <v>108</v>
       </c>
       <c r="T21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO21" t="s">
         <v>108</v>
@@ -5532,13 +5484,13 @@
         <v>108</v>
       </c>
       <c r="BU21" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="BV21" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW21" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:75">
@@ -5597,58 +5549,58 @@
         <v>108</v>
       </c>
       <c r="S22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK22" t="s">
         <v>108</v>
@@ -5759,13 +5711,13 @@
         <v>108</v>
       </c>
       <c r="BU22" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV22" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="BW22" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:75">
@@ -5830,55 +5782,55 @@
         <v>108</v>
       </c>
       <c r="U23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL23" t="s">
         <v>108</v>
@@ -5986,13 +5938,13 @@
         <v>108</v>
       </c>
       <c r="BU23" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="BV23" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW23" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:75">
@@ -6051,49 +6003,49 @@
         <v>108</v>
       </c>
       <c r="S24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH24" t="s">
         <v>108</v>
@@ -6102,10 +6054,10 @@
         <v>108</v>
       </c>
       <c r="AJ24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL24" t="s">
         <v>108</v>
@@ -6213,13 +6165,13 @@
         <v>108</v>
       </c>
       <c r="BU24" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="BV24" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="BW24" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:75">
@@ -6278,58 +6230,58 @@
         <v>108</v>
       </c>
       <c r="S25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK25" t="s">
         <v>108</v>
@@ -6440,13 +6392,13 @@
         <v>108</v>
       </c>
       <c r="BU25" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="BV25" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="BW25" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:75">
@@ -6511,64 +6463,64 @@
         <v>108</v>
       </c>
       <c r="U26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO26" t="s">
         <v>108</v>
@@ -6667,13 +6619,13 @@
         <v>108</v>
       </c>
       <c r="BU26" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="BV26" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="BW26" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:75">
@@ -6738,55 +6690,55 @@
         <v>108</v>
       </c>
       <c r="U27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL27" t="s">
         <v>108</v>
@@ -6894,13 +6846,13 @@
         <v>108</v>
       </c>
       <c r="BU27" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BV27" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="BW27" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:75">
@@ -6959,58 +6911,58 @@
         <v>108</v>
       </c>
       <c r="S28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK28" t="s">
         <v>108</v>
@@ -7121,13 +7073,13 @@
         <v>108</v>
       </c>
       <c r="BU28" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV28" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="BW28" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:75">
@@ -7186,55 +7138,55 @@
         <v>108</v>
       </c>
       <c r="S29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T29" t="s">
         <v>108</v>
       </c>
       <c r="U29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ29" t="s">
         <v>108</v>
@@ -7348,13 +7300,13 @@
         <v>108</v>
       </c>
       <c r="BU29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV29" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW29" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:75">
@@ -7413,58 +7365,58 @@
         <v>108</v>
       </c>
       <c r="S30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK30" t="s">
         <v>108</v>
@@ -7575,13 +7527,13 @@
         <v>108</v>
       </c>
       <c r="BU30" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BV30" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW30" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:75">
@@ -7640,64 +7592,64 @@
         <v>108</v>
       </c>
       <c r="S31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM31" t="s">
         <v>108</v>
@@ -7802,13 +7754,13 @@
         <v>108</v>
       </c>
       <c r="BU31" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV31" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="BW31" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:75">
@@ -7867,58 +7819,58 @@
         <v>108</v>
       </c>
       <c r="S32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK32" t="s">
         <v>108</v>
@@ -8029,13 +7981,13 @@
         <v>108</v>
       </c>
       <c r="BU32" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BV32" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW32" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:75">
@@ -8097,55 +8049,55 @@
         <v>108</v>
       </c>
       <c r="T33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK33" t="s">
         <v>108</v>
@@ -8256,13 +8208,13 @@
         <v>108</v>
       </c>
       <c r="BU33" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="BV33" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW33" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:75">
@@ -8315,25 +8267,25 @@
         <v>108</v>
       </c>
       <c r="Q34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R34" t="s">
         <v>108</v>
       </c>
       <c r="S34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X34" t="s">
         <v>108</v>
@@ -8342,37 +8294,37 @@
         <v>108</v>
       </c>
       <c r="Z34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK34" t="s">
         <v>108</v>
@@ -8483,13 +8435,13 @@
         <v>108</v>
       </c>
       <c r="BU34" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="BV34" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="BW34" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Wheat_flour_(low_quality)_tukey_classification_matrix.xlsx
+++ b/outputs/Wheat_flour_(low_quality)_tukey_classification_matrix.xlsx
@@ -340,7 +340,7 @@
     <t>Zabul</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>0%</t>
